--- a/data/trans_camb/P19C02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C02-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 13,55</t>
+          <t>-1,11; 13,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,17; 22,34</t>
+          <t>8,07; 22,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,34; 26,92</t>
+          <t>13,94; 27,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 6,91</t>
+          <t>-9,96; 6,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 10,3</t>
+          <t>-5,7; 10,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 20,52</t>
+          <t>6,15; 20,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 8,65</t>
+          <t>-2,25; 8,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 14,92</t>
+          <t>4,1; 15,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,71; 22,42</t>
+          <t>12,77; 22,64</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 43,74</t>
+          <t>-2,95; 44,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,07; 71,92</t>
+          <t>21,03; 70,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,58; 87,27</t>
+          <t>35,04; 88,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 18,86</t>
+          <t>-21,55; 17,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 27,2</t>
+          <t>-12,45; 28,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,06; 55,24</t>
+          <t>12,96; 54,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 25,01</t>
+          <t>-5,61; 24,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,25; 42,74</t>
+          <t>10,03; 43,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,4; 64,6</t>
+          <t>31,31; 64,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 10,37</t>
+          <t>-5,78; 10,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 10,85</t>
+          <t>-5,92; 10,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,1; 24,15</t>
+          <t>9,25; 24,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 9,27</t>
+          <t>-7,24; 8,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 15,35</t>
+          <t>0,43; 15,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,99; 26,98</t>
+          <t>12,73; 26,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 7,11</t>
+          <t>-3,66; 7,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 10,41</t>
+          <t>-1,39; 10,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,79; 23,36</t>
+          <t>12,57; 22,96</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 29,42</t>
+          <t>-13,14; 30,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 30,91</t>
+          <t>-13,92; 30,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,88; 69,99</t>
+          <t>21,5; 74,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 26,34</t>
+          <t>-16,36; 23,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 41,91</t>
+          <t>0,96; 45,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,71; 80,78</t>
+          <t>28,67; 77,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 20,45</t>
+          <t>-8,76; 20,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 28,73</t>
+          <t>-3,26; 29,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,26; 65,73</t>
+          <t>29,93; 64,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 6,3</t>
+          <t>-5,77; 6,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 7,46</t>
+          <t>-5,84; 7,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 19,09</t>
+          <t>-21,91; 19,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 7,42</t>
+          <t>-13,32; 7,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 14,0</t>
+          <t>-7,06; 15,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,52; 31,14</t>
+          <t>12,02; 32,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 4,34</t>
+          <t>-5,87; 4,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 7,06</t>
+          <t>-3,7; 7,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 21,24</t>
+          <t>-17,85; 20,48</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 23,24</t>
+          <t>-16,89; 23,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 27,39</t>
+          <t>-17,3; 25,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,13; 63,64</t>
+          <t>-65,22; 64,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 26,1</t>
+          <t>-31,26; 27,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,48; 46,73</t>
+          <t>-18,54; 54,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,45; 112,8</t>
+          <t>28,19; 112,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 14,63</t>
+          <t>-16,51; 17,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 25,11</t>
+          <t>-11,01; 25,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 69,5</t>
+          <t>-53,36; 66,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 4,85</t>
+          <t>-3,29; 5,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 10,16</t>
+          <t>1,93; 10,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,09; 21,72</t>
+          <t>12,46; 21,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 11,62</t>
+          <t>0,96; 11,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,56; 14,71</t>
+          <t>4,26; 14,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,26; 50,88</t>
+          <t>17,38; 49,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 6,49</t>
+          <t>0,09; 6,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 11,19</t>
+          <t>4,47; 11,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,96; 36,93</t>
+          <t>16,99; 42,1</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 22,29</t>
+          <t>-12,49; 23,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,19; 46,55</t>
+          <t>7,41; 49,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51,12; 100,58</t>
+          <t>47,57; 95,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,61; 43,48</t>
+          <t>3,55; 43,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,92; 54,7</t>
+          <t>13,38; 56,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,91; 190,6</t>
+          <t>56,26; 188,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 26,6</t>
+          <t>0,24; 27,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,33; 45,99</t>
+          <t>15,87; 45,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>62,52; 145,31</t>
+          <t>63,78; 165,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 7,78</t>
+          <t>-4,88; 8,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,7; 20,77</t>
+          <t>7,34; 20,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,41; 27,18</t>
+          <t>13,66; 27,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 7,56</t>
+          <t>-3,29; 7,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,15; 14,76</t>
+          <t>3,75; 15,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 18,99</t>
+          <t>3,17; 18,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 6,16</t>
+          <t>-2,19; 6,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,4; 15,09</t>
+          <t>6,6; 15,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,5; 20,12</t>
+          <t>8,05; 20,19</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 57,3</t>
+          <t>-21,6; 58,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>36,16; 153,8</t>
+          <t>32,28; 150,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>63,25; 201,84</t>
+          <t>62,21; 196,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 36,96</t>
+          <t>-12,12; 35,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,07; 71,05</t>
+          <t>14,13; 72,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,63; 88,95</t>
+          <t>13,26; 89,8</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 33,11</t>
+          <t>-9,06; 32,69</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>25,92; 79,41</t>
+          <t>27,74; 81,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35,82; 103,43</t>
+          <t>35,83; 103,82</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 5,28</t>
+          <t>-12,47; 4,45</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 8,13</t>
+          <t>-7,77; 8,61</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11,31; 36,2</t>
+          <t>11,57; 35,93</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 5,99</t>
+          <t>-2,34; 5,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,8; 12,37</t>
+          <t>4,13; 12,72</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,29; 23,56</t>
+          <t>14,79; 23,42</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 4,57</t>
+          <t>-3,26; 4,19</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,93; 10,22</t>
+          <t>3,21; 10,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16,3; 25,44</t>
+          <t>16,57; 25,22</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-35,22; 20,33</t>
+          <t>-35,73; 17,47</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 29,78</t>
+          <t>-22,33; 33,86</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>34,48; 135,77</t>
+          <t>31,95; 131,85</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 27,07</t>
+          <t>-9,25; 25,92</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>14,78; 57,12</t>
+          <t>15,36; 58,23</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>55,67; 109,31</t>
+          <t>57,98; 108,7</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 19,78</t>
+          <t>-12,37; 18,24</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>10,44; 43,68</t>
+          <t>11,63; 44,81</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>61,5; 108,8</t>
+          <t>60,58; 108,08</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,42</t>
+          <t>-1,66; 3,2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,78</t>
+          <t>3,58; 8,79</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,58; 19,24</t>
+          <t>3,05; 19,22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,53</t>
+          <t>-0,28; 4,51</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,78; 10,53</t>
+          <t>5,46; 10,66</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,72; 31,09</t>
+          <t>16,55; 30,63</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,28</t>
+          <t>-0,16; 3,14</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5,39; 9,14</t>
+          <t>5,46; 8,94</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13,25; 22,38</t>
+          <t>12,55; 22,77</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 12,32</t>
+          <t>-5,57; 11,73</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>11,66; 32,76</t>
+          <t>11,75; 32,41</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13,18; 69,45</t>
+          <t>11,61; 68,46</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 16,24</t>
+          <t>-0,9; 16,14</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>18,98; 37,97</t>
+          <t>17,96; 38,34</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>55,47; 101,99</t>
+          <t>54,83; 106,0</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 11,89</t>
+          <t>-0,6; 11,05</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>17,72; 32,19</t>
+          <t>18,24; 31,83</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>45,34; 78,54</t>
+          <t>42,67; 78,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C02-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20,18</t>
+          <t>21,37</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,66</t>
+          <t>13,64</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,53</t>
+          <t>18,15</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 13,53</t>
+          <t>-1,74; 13,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,07; 22,19</t>
+          <t>7,45; 21,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,94; 27,21</t>
+          <t>14,79; 27,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 6,6</t>
+          <t>-9,6; 6,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 10,49</t>
+          <t>-5,66; 10,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 20,1</t>
+          <t>6,35; 20,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 8,57</t>
+          <t>-2,34; 8,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 15,07</t>
+          <t>4,06; 14,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,77; 22,64</t>
+          <t>12,89; 22,91</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 44,13</t>
+          <t>-4,37; 41,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,03; 70,72</t>
+          <t>19,44; 69,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,04; 88,26</t>
+          <t>37,61; 88,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,55; 17,18</t>
+          <t>-20,77; 18,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 28,22</t>
+          <t>-12,6; 28,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,96; 54,03</t>
+          <t>14,15; 55,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 24,56</t>
+          <t>-5,96; 24,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 43,21</t>
+          <t>10,25; 41,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,31; 64,73</t>
+          <t>30,96; 65,94</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>16,92</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,89</t>
+          <t>19,18</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17,95</t>
+          <t>17,94</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 10,59</t>
+          <t>-5,87; 9,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 10,53</t>
+          <t>-6,42; 9,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,25; 24,95</t>
+          <t>9,12; 24,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 8,2</t>
+          <t>-7,38; 8,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 15,72</t>
+          <t>0,09; 14,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,73; 26,57</t>
+          <t>11,75; 25,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 7,28</t>
+          <t>-4,29; 7,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 10,49</t>
+          <t>-1,16; 10,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,57; 22,96</t>
+          <t>12,77; 22,61</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 30,89</t>
+          <t>-13,34; 27,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 30,46</t>
+          <t>-15,07; 27,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,5; 74,71</t>
+          <t>20,59; 68,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 23,13</t>
+          <t>-16,91; 24,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 45,62</t>
+          <t>0,28; 42,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,67; 77,05</t>
+          <t>27,66; 73,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 20,27</t>
+          <t>-10,44; 19,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 29,89</t>
+          <t>-2,68; 29,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,93; 64,15</t>
+          <t>30,15; 63,35</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>18,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,0</t>
+          <t>21,74</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,88</t>
+          <t>19,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 6,43</t>
+          <t>-5,55; 6,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 7,09</t>
+          <t>-5,52; 7,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,91; 19,25</t>
+          <t>11,54; 24,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 7,83</t>
+          <t>-12,16; 6,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 15,38</t>
+          <t>-8,57; 14,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,02; 32,19</t>
+          <t>12,56; 32,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 4,93</t>
+          <t>-5,47; 4,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 7,26</t>
+          <t>-4,45; 7,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 20,48</t>
+          <t>14,38; 25,21</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-1,36%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>60,9%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 23,84</t>
+          <t>-16,55; 22,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 25,95</t>
+          <t>-16,33; 29,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,22; 64,6</t>
+          <t>33,27; 90,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,26; 27,55</t>
+          <t>-30,23; 24,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 54,92</t>
+          <t>-22,22; 49,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,19; 112,97</t>
+          <t>31,25; 120,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 17,15</t>
+          <t>-16,13; 17,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 25,05</t>
+          <t>-12,62; 26,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,36; 66,43</t>
+          <t>41,16; 86,7</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,13</t>
+          <t>16,99</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,52</t>
+          <t>19,7</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24,12</t>
+          <t>18,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 5,07</t>
+          <t>-3,74; 4,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 10,72</t>
+          <t>2,08; 10,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,46; 21,14</t>
+          <t>12,29; 21,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 11,39</t>
+          <t>1,35; 11,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 14,72</t>
+          <t>4,63; 15,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,38; 49,13</t>
+          <t>14,55; 24,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 6,56</t>
+          <t>-0,14; 6,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 11,15</t>
+          <t>4,59; 11,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,99; 42,1</t>
+          <t>14,87; 21,41</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>105,35%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>70,46%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 23,49</t>
+          <t>-13,86; 19,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,41; 49,99</t>
+          <t>7,92; 48,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,57; 95,34</t>
+          <t>47,86; 99,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,55; 43,91</t>
+          <t>4,09; 44,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,38; 56,45</t>
+          <t>14,54; 56,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,26; 188,88</t>
+          <t>45,43; 95,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 27,31</t>
+          <t>-0,5; 27,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,87; 45,67</t>
+          <t>16,86; 47,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>63,78; 165,49</t>
+          <t>53,43; 89,04</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20,45</t>
+          <t>19,58</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,49</t>
+          <t>19,13</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15,29</t>
+          <t>19,07</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 8,07</t>
+          <t>-4,33; 7,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,34; 20,98</t>
+          <t>7,09; 20,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,66; 27,3</t>
+          <t>13,21; 26,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 7,58</t>
+          <t>-3,66; 7,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,75; 15,11</t>
+          <t>3,9; 15,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 18,94</t>
+          <t>14,37; 24,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 6,25</t>
+          <t>-2,07; 6,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,6; 15,41</t>
+          <t>6,4; 15,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,05; 20,19</t>
+          <t>14,61; 23,07</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115,76%</t>
+          <t>110,87%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 58,43</t>
+          <t>-20,09; 58,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>32,28; 150,69</t>
+          <t>30,43; 146,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62,21; 196,18</t>
+          <t>58,19; 188,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 35,69</t>
+          <t>-13,39; 35,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>14,13; 72,2</t>
+          <t>13,77; 72,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,26; 89,8</t>
+          <t>51,42; 120,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 32,69</t>
+          <t>-8,57; 33,02</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27,74; 81,77</t>
+          <t>26,9; 81,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35,83; 103,82</t>
+          <t>61,32; 122,74</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23,83</t>
+          <t>25,8</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,04</t>
+          <t>20,02</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20,58</t>
+          <t>21,51</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 4,45</t>
+          <t>-11,49; 4,59</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 8,61</t>
+          <t>-8,25; 8,92</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11,57; 35,93</t>
+          <t>12,2; 37,11</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 5,67</t>
+          <t>-2,52; 5,42</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,13; 12,72</t>
+          <t>3,71; 12,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,79; 23,42</t>
+          <t>15,67; 24,27</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 4,19</t>
+          <t>-2,69; 4,44</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,21; 10,49</t>
+          <t>2,71; 10,48</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16,57; 25,22</t>
+          <t>17,38; 25,82</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-35,73; 17,47</t>
+          <t>-33,55; 17,44</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 33,86</t>
+          <t>-22,25; 33,14</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31,95; 131,85</t>
+          <t>36,0; 140,67</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 25,92</t>
+          <t>-9,92; 24,58</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>15,36; 58,23</t>
+          <t>14,53; 57,0</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>57,98; 108,7</t>
+          <t>59,88; 112,58</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 18,24</t>
+          <t>-10,06; 18,89</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>11,63; 44,81</t>
+          <t>10,39; 45,2</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>60,58; 108,08</t>
+          <t>65,21; 112,05</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14,89</t>
+          <t>18,54</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,77</t>
+          <t>19,63</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17,92</t>
+          <t>19,1</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,2</t>
+          <t>-1,76; 3,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,79</t>
+          <t>3,25; 8,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,05; 19,22</t>
+          <t>15,89; 21,05</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,51</t>
+          <t>-0,42; 4,47</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,66</t>
+          <t>5,47; 10,58</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,55; 30,63</t>
+          <t>17,18; 21,82</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,14</t>
+          <t>-0,35; 3,39</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5,46; 8,94</t>
+          <t>5,06; 9,02</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,55; 22,77</t>
+          <t>17,26; 20,79</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>66,04%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 11,73</t>
+          <t>-5,92; 12,76</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>11,75; 32,41</t>
+          <t>10,93; 31,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11,61; 68,46</t>
+          <t>51,89; 76,67</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 16,14</t>
+          <t>-1,41; 15,88</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>17,96; 38,34</t>
+          <t>17,85; 37,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>54,83; 106,0</t>
+          <t>56,08; 79,04</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 11,05</t>
+          <t>-1,21; 12,14</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>18,24; 31,83</t>
+          <t>16,74; 32,04</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>42,67; 78,93</t>
+          <t>56,96; 74,14</t>
         </is>
       </c>
     </row>
